--- a/gram_panchayat_reservation.xlsx
+++ b/gram_panchayat_reservation.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anind\gram_panchayat\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56375533-E4A0-409B-A7CA-6A918370EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
-    <sheet r:id="rId2" sheetId="2" name="gp_code"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="gp_code" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="381">
   <si>
     <t>code</t>
   </si>
@@ -615,13 +621,555 @@
   </si>
   <si>
     <t>Vaswi</t>
+  </si>
+  <si>
+    <t>Pes</t>
+  </si>
+  <si>
+    <t>Hanriya</t>
+  </si>
+  <si>
+    <t>Dohra</t>
+  </si>
+  <si>
+    <t>Ichuakarna</t>
+  </si>
+  <si>
+    <t>Ordo</t>
+  </si>
+  <si>
+    <t>Kosla</t>
+  </si>
+  <si>
+    <t>Nardiganj</t>
+  </si>
+  <si>
+    <t>Kahuara</t>
+  </si>
+  <si>
+    <t>Parman</t>
+  </si>
+  <si>
+    <t>Nenaura</t>
+  </si>
+  <si>
+    <t>Masaurha</t>
+  </si>
+  <si>
+    <t>Jamuawan Patwasarai</t>
+  </si>
+  <si>
+    <t>Nonoura</t>
+  </si>
+  <si>
+    <t>Jhunathi</t>
+  </si>
+  <si>
+    <t>Oraina</t>
+  </si>
+  <si>
+    <t>Bhadokhara</t>
+  </si>
+  <si>
+    <t>Mahuli</t>
+  </si>
+  <si>
+    <t>Samai</t>
+  </si>
+  <si>
+    <t>Bhagwan Pur</t>
+  </si>
+  <si>
+    <t>Kena</t>
+  </si>
+  <si>
+    <t>Kharant</t>
+  </si>
+  <si>
+    <t>Sonsihari</t>
+  </si>
+  <si>
+    <t>Aanti</t>
+  </si>
+  <si>
+    <t>Kadirganj</t>
+  </si>
+  <si>
+    <t>Loharpura</t>
+  </si>
+  <si>
+    <t>Paura</t>
+  </si>
+  <si>
+    <t>Birnanwan</t>
+  </si>
+  <si>
+    <t>Manjaur</t>
+  </si>
+  <si>
+    <t>Mohiuddinpur</t>
+  </si>
+  <si>
+    <t>Saur</t>
+  </si>
+  <si>
+    <t>Paingari</t>
+  </si>
+  <si>
+    <t>Makanpur</t>
+  </si>
+  <si>
+    <t>Kutri</t>
+  </si>
+  <si>
+    <t>Kochgawan</t>
+  </si>
+  <si>
+    <t>Chakwai</t>
+  </si>
+  <si>
+    <t>Mosama</t>
+  </si>
+  <si>
+    <t>Thera</t>
+  </si>
+  <si>
+    <t>Apsand</t>
+  </si>
+  <si>
+    <t>Shahpur</t>
+  </si>
+  <si>
+    <t>Dosut</t>
+  </si>
+  <si>
+    <t>Hajipur</t>
+  </si>
+  <si>
+    <t>Baghi Bardiha</t>
+  </si>
+  <si>
+    <t>Belar</t>
+  </si>
+  <si>
+    <t>Khakhari</t>
+  </si>
+  <si>
+    <t>Subhanpur</t>
+  </si>
+  <si>
+    <t>Parwati</t>
+  </si>
+  <si>
+    <t>Rewara Jagdishpur</t>
+  </si>
+  <si>
+    <t>Chandi Nawan</t>
+  </si>
+  <si>
+    <t>Konandpur</t>
+  </si>
+  <si>
+    <t>Poksi</t>
+  </si>
+  <si>
+    <t>Dumrawan</t>
+  </si>
+  <si>
+    <t>Aruri</t>
+  </si>
+  <si>
+    <t>Dheodha</t>
+  </si>
+  <si>
+    <t>Ukaura</t>
+  </si>
+  <si>
+    <t>Pakribarawan South</t>
+  </si>
+  <si>
+    <t>Pakribarawan North</t>
+  </si>
+  <si>
+    <t>Budhauli</t>
+  </si>
+  <si>
+    <t>Kabla</t>
+  </si>
+  <si>
+    <t>Jiuri</t>
+  </si>
+  <si>
+    <t>Datraul</t>
+  </si>
+  <si>
+    <t>Belkhunda</t>
+  </si>
+  <si>
+    <t>Dhorah</t>
+  </si>
+  <si>
+    <t>Dhamaul</t>
+  </si>
+  <si>
+    <t>Gulni</t>
+  </si>
+  <si>
+    <t>Kharsari</t>
+  </si>
+  <si>
+    <t>Chhabail</t>
+  </si>
+  <si>
+    <t>Darawan</t>
+  </si>
+  <si>
+    <t>Manjhila</t>
+  </si>
+  <si>
+    <t>Pali</t>
+  </si>
+  <si>
+    <t>Kewali</t>
+  </si>
+  <si>
+    <t>Nawadih</t>
+  </si>
+  <si>
+    <t>Pandey Gangaut</t>
+  </si>
+  <si>
+    <t>Dewangarh</t>
+  </si>
+  <si>
+    <t>Sekhodewra</t>
+  </si>
+  <si>
+    <t>Sarauni</t>
+  </si>
+  <si>
+    <t>Paharpur</t>
+  </si>
+  <si>
+    <t>Kauakole</t>
+  </si>
+  <si>
+    <t>Mahudar</t>
+  </si>
+  <si>
+    <t>Lalpur</t>
+  </si>
+  <si>
+    <t>Ohari</t>
+  </si>
+  <si>
+    <t>Chhanaun</t>
+  </si>
+  <si>
+    <t>Bhikhanpur</t>
+  </si>
+  <si>
+    <t>Dumari</t>
+  </si>
+  <si>
+    <t>Kunj</t>
+  </si>
+  <si>
+    <t>Samahrigadh</t>
+  </si>
+  <si>
+    <t>Marui</t>
+  </si>
+  <si>
+    <t>Nazardih</t>
+  </si>
+  <si>
+    <t>Madra</t>
+  </si>
+  <si>
+    <t>Bhatta</t>
+  </si>
+  <si>
+    <t>Morawan</t>
+  </si>
+  <si>
+    <t>Roh</t>
+  </si>
+  <si>
+    <t>Koshirukhi</t>
+  </si>
+  <si>
+    <t>Siur</t>
+  </si>
+  <si>
+    <t>Sughri</t>
+  </si>
+  <si>
+    <t>Sarkanda</t>
+  </si>
+  <si>
+    <t>Madhopur</t>
+  </si>
+  <si>
+    <t>Bhawan Pur</t>
+  </si>
+  <si>
+    <t>Baksauti</t>
+  </si>
+  <si>
+    <t>Gobindpur</t>
+  </si>
+  <si>
+    <t>Bishun Pur</t>
+  </si>
+  <si>
+    <t>Baniya Bigha</t>
+  </si>
+  <si>
+    <t>Budhwara</t>
+  </si>
+  <si>
+    <t>Sakarpura</t>
+  </si>
+  <si>
+    <t>Teyar</t>
+  </si>
+  <si>
+    <t>Makhar</t>
+  </si>
+  <si>
+    <t>Barail</t>
+  </si>
+  <si>
+    <t>Parato Karhari</t>
+  </si>
+  <si>
+    <t>Pachganwa</t>
+  </si>
+  <si>
+    <t>Pachrukhi</t>
+  </si>
+  <si>
+    <t>Paijuna</t>
+  </si>
+  <si>
+    <t>Gobind Bigha</t>
+  </si>
+  <si>
+    <t>Baksanda</t>
+  </si>
+  <si>
+    <t>Fatehpur</t>
+  </si>
+  <si>
+    <t>Budhuwa</t>
+  </si>
+  <si>
+    <t>Baliya Buzurg</t>
+  </si>
+  <si>
+    <t>Kulana</t>
+  </si>
+  <si>
+    <t>Panti</t>
+  </si>
+  <si>
+    <t>Ledaha</t>
+  </si>
+  <si>
+    <t>Bhanail Lodipur</t>
+  </si>
+  <si>
+    <t>Malikpur Nemdarganj</t>
+  </si>
+  <si>
+    <t>Barew</t>
+  </si>
+  <si>
+    <t>Pacharha</t>
+  </si>
+  <si>
+    <t>Chhatihar</t>
+  </si>
+  <si>
+    <t>Dhanwa</t>
+  </si>
+  <si>
+    <t>Bagodar</t>
+  </si>
+  <si>
+    <t>Sonsa</t>
+  </si>
+  <si>
+    <t>Kaithir</t>
+  </si>
+  <si>
+    <t>Hadsa</t>
+  </si>
+  <si>
+    <t>Dona</t>
+  </si>
+  <si>
+    <t>Chitarghatti</t>
+  </si>
+  <si>
+    <t>Tungi</t>
+  </si>
+  <si>
+    <t>Babhnaur</t>
+  </si>
+  <si>
+    <t>Punthar</t>
+  </si>
+  <si>
+    <t>Punaul</t>
+  </si>
+  <si>
+    <t>Shekhpura</t>
+  </si>
+  <si>
+    <t>Jamuara</t>
+  </si>
+  <si>
+    <t>Pali Khurd</t>
+  </si>
+  <si>
+    <t>Khanwan</t>
+  </si>
+  <si>
+    <t>Konibar</t>
+  </si>
+  <si>
+    <t>Narhat</t>
+  </si>
+  <si>
+    <t>Saidapur Gowasa</t>
+  </si>
+  <si>
+    <t>Mirzapur</t>
+  </si>
+  <si>
+    <t>Bisiyait</t>
+  </si>
+  <si>
+    <t>Badosar</t>
+  </si>
+  <si>
+    <t>Tetaria</t>
+  </si>
+  <si>
+    <t>Meskaur</t>
+  </si>
+  <si>
+    <t>Biju Bigha</t>
+  </si>
+  <si>
+    <t>Barat</t>
+  </si>
+  <si>
+    <t>Sahwajpur Saray</t>
+  </si>
+  <si>
+    <t>Rasalpura</t>
+  </si>
+  <si>
+    <t>Ankri Pandeybigha</t>
+  </si>
+  <si>
+    <t>Laund</t>
+  </si>
+  <si>
+    <t>Bargawn</t>
+  </si>
+  <si>
+    <t>Upardih</t>
+  </si>
+  <si>
+    <t>Sanrh Majhagawan</t>
+  </si>
+  <si>
+    <t>Abdul</t>
+  </si>
+  <si>
+    <t>Chaukiya</t>
+  </si>
+  <si>
+    <t>Khatangi</t>
+  </si>
+  <si>
+    <t>Ghaghat</t>
+  </si>
+  <si>
+    <t>Akauna</t>
+  </si>
+  <si>
+    <t>Chaubey</t>
+  </si>
+  <si>
+    <t>Sirdalla</t>
+  </si>
+  <si>
+    <t>Bandhi</t>
+  </si>
+  <si>
+    <t>Dhiraundh</t>
+  </si>
+  <si>
+    <t>Khanpura</t>
+  </si>
+  <si>
+    <t>Rajan</t>
+  </si>
+  <si>
+    <t>Hardia</t>
+  </si>
+  <si>
+    <t>Dhamni</t>
+  </si>
+  <si>
+    <t>Chitarkoli</t>
+  </si>
+  <si>
+    <t>Sirodabar</t>
+  </si>
+  <si>
+    <t>Jogya Maran</t>
+  </si>
+  <si>
+    <t>Bahadurpur</t>
+  </si>
+  <si>
+    <t>Amawan East</t>
+  </si>
+  <si>
+    <t>Amawan West</t>
+  </si>
+  <si>
+    <t>Lengura</t>
+  </si>
+  <si>
+    <t>Andharbari</t>
+  </si>
+  <si>
+    <t>Murhaina</t>
+  </si>
+  <si>
+    <t>Farka Buzurg</t>
+  </si>
+  <si>
+    <t>Sabaiyatand</t>
+  </si>
+  <si>
+    <t>Rajauli East</t>
+  </si>
+  <si>
+    <t>Rajauli West</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -655,43 +1203,43 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="medium">
-        <color rgb="FFcccccc"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -702,50 +1250,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -756,10 +1316,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -797,71 +1357,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -889,7 +1449,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -912,11 +1472,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -925,13 +1485,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -941,7 +1501,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -950,7 +1510,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -959,7 +1519,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -967,10 +1527,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -1035,30 +1595,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B411"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B593"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,3284 +1626,4740 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>132830</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A3" s="6">
+    <row r="3" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>132830</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A4" s="6">
+    <row r="4" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>132844</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A5" s="6">
+    <row r="5" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>132830</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>132831</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>132832</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A8" s="6">
+    <row r="8" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>132841</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A9" s="6">
+    <row r="9" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>132833</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A10" s="6">
+    <row r="10" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>132834</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A11" s="6">
+    <row r="11" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>132835</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A12" s="6">
+    <row r="12" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>132835</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A13" s="6">
+    <row r="13" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
         <v>132845</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A14" s="6">
+    <row r="14" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>132836</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A15" s="6">
+    <row r="15" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
         <v>132837</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A16" s="6">
+    <row r="16" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>132838</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A17" s="6">
+    <row r="17" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>250914</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A18" s="6">
+    <row r="18" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>132831</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A19" s="6">
+    <row r="19" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>132839</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A20" s="6">
+    <row r="20" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>132832</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A21" s="6">
+    <row r="21" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>132840</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A22" s="6">
+    <row r="22" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>132841</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A23" s="6">
+    <row r="23" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>132842</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A24" s="6">
+    <row r="24" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>132843</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A25" s="6">
+    <row r="25" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>132844</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:2" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>132845</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A27" s="6">
+    <row r="27" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>132861</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A28" s="6">
+    <row r="28" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>132847</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A29" s="6">
+    <row r="29" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>132846</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A30" s="6">
+    <row r="30" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
         <v>132848</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A31" s="6">
+    <row r="31" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5">
         <v>132837</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A32" s="6">
+    <row r="32" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5">
         <v>132849</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A33" s="6">
+    <row r="33" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5">
         <v>132834</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A34" s="6">
+    <row r="34" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5">
         <v>132873</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A35" s="6">
+    <row r="35" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5">
         <v>132850</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A36" s="6">
+    <row r="36" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5">
         <v>132840</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A37" s="6">
+    <row r="37" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5">
         <v>132851</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A38" s="6">
+    <row r="38" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5">
         <v>132857</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A39" s="6">
+    <row r="39" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5">
         <v>132857</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A40" s="6">
+    <row r="40" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5">
         <v>132861</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A41" s="6">
+    <row r="41" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5">
         <v>132852</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A42" s="6">
+    <row r="42" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5">
         <v>132853</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A43" s="6">
+    <row r="43" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5">
         <v>132854</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A44" s="6">
+    <row r="44" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5">
         <v>132840</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A45" s="6">
+    <row r="45" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5">
         <v>132845</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A46" s="6">
+    <row r="46" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5">
         <v>132832</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A47" s="6">
+    <row r="47" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5">
         <v>132831</v>
       </c>
-      <c r="B47" s="7" t="s">
+      <c r="B47" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A48" s="6">
+    <row r="48" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5">
         <v>132866</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A49" s="6">
+    <row r="49" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5">
         <v>132855</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A50" s="6">
+    <row r="50" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="5">
         <v>132831</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A51" s="6">
+    <row r="51" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="5">
         <v>132856</v>
       </c>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A52" s="6">
+    <row r="52" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="5">
         <v>132843</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A53" s="6">
+    <row r="53" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="5">
         <v>132830</v>
       </c>
-      <c r="B53" s="7" t="s">
+      <c r="B53" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A54" s="6">
+    <row r="54" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="5">
         <v>132868</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A55" s="6">
+    <row r="55" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="5">
         <v>132857</v>
       </c>
-      <c r="B55" s="7" t="s">
+      <c r="B55" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A56" s="6">
+    <row r="56" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="5">
         <v>132866</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A57" s="6">
+    <row r="57" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="5">
         <v>132858</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A58" s="6">
+    <row r="58" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="5">
         <v>132834</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A59" s="6">
+    <row r="59" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="5">
         <v>132842</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A60" s="6">
+    <row r="60" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="5">
         <v>132859</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A61" s="6">
+    <row r="61" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5">
         <v>132859</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A62" s="6">
+    <row r="62" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="5">
         <v>132860</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A63" s="6">
+    <row r="63" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5">
         <v>132861</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A64" s="6">
+    <row r="64" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="5">
         <v>132862</v>
       </c>
-      <c r="B64" s="7" t="s">
+      <c r="B64" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A65" s="6">
+    <row r="65" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="5">
         <v>132863</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A66" s="6">
+    <row r="66" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="5">
         <v>132866</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A67" s="6">
+    <row r="67" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="5">
         <v>132876</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A68" s="6">
+    <row r="68" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="5">
         <v>132856</v>
       </c>
-      <c r="B68" s="7" t="s">
+      <c r="B68" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A69" s="6">
+    <row r="69" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="5">
         <v>132864</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A70" s="6">
+    <row r="70" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="5">
         <v>132865</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A71" s="6">
+    <row r="71" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="5">
         <v>132856</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A72" s="6">
+    <row r="72" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="5">
         <v>132866</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B72" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A73" s="6">
+    <row r="73" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="5">
         <v>132867</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A74" s="6">
+    <row r="74" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="5">
         <v>132868</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A75" s="6">
+    <row r="75" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="5">
         <v>132834</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A76" s="6">
+    <row r="76" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="5">
         <v>132871</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="B76" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A77" s="6">
+    <row r="77" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="5">
         <v>132869</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A78" s="6">
+    <row r="78" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="5">
         <v>132880</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A79" s="6">
+    <row r="79" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="5">
         <v>132871</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A80" s="6">
+    <row r="80" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="5">
         <v>132870</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A81" s="6">
+    <row r="81" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="5">
         <v>132872</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A82" s="6">
+    <row r="82" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="5">
         <v>132873</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A83" s="6">
+    <row r="83" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="5">
         <v>132848</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="B83" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A84" s="6">
+    <row r="84" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="5">
         <v>132857</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A85" s="6">
+    <row r="85" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="5">
         <v>132833</v>
       </c>
-      <c r="B85" s="7" t="s">
+      <c r="B85" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A86" s="6">
+    <row r="86" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="5">
         <v>132867</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A87" s="6">
+    <row r="87" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="5">
         <v>132874</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="B87" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A88" s="6">
+    <row r="88" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="5">
         <v>132866</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A89" s="6">
+    <row r="89" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="5">
         <v>132875</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A90" s="6">
+    <row r="90" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="5">
         <v>132876</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A91" s="6">
+    <row r="91" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="5">
         <v>132877</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="6" t="s">
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A92" s="6">
+    <row r="92" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="5">
         <v>132835</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A93" s="6">
+    <row r="93" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="5">
         <v>132878</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="6" t="s">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A94" s="6">
+    <row r="94" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="5">
         <v>132879</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A95" s="6">
+    <row r="95" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="5">
         <v>132854</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A96" s="6">
+    <row r="96" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5">
         <v>132869</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B96" s="6" t="s">
         <v>45</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A97" s="6">
+    <row r="97" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="5">
         <v>132880</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A98" s="6">
+    <row r="98" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="5">
         <v>132867</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A99" s="6">
+    <row r="99" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="5">
         <v>132860</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A100" s="6">
+    <row r="100" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5">
         <v>132881</v>
       </c>
-      <c r="B100" s="7" t="s">
+      <c r="B100" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A101" s="6">
+    <row r="101" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="5">
         <v>132946</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A102" s="6">
+    <row r="102" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="5">
         <v>132926</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A103" s="6">
+    <row r="103" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="5">
         <v>132926</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A104" s="6">
+    <row r="104" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="5">
         <v>132926</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B104" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A105" s="6">
+    <row r="105" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="5">
         <v>132931</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A106" s="6">
+    <row r="106" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="5">
         <v>132924</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A107" s="6">
+    <row r="107" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="5">
         <v>132925</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A108" s="6">
+    <row r="108" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5">
         <v>132925</v>
       </c>
-      <c r="B108" s="7" t="s">
+      <c r="B108" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A109" s="6">
+    <row r="109" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="5">
         <v>132952</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A110" s="6">
+    <row r="110" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="5">
         <v>132927</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A111" s="6">
+    <row r="111" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="5">
         <v>132928</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A112" s="6">
+    <row r="112" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="5">
         <v>132929</v>
       </c>
-      <c r="B112" s="7" t="s">
+      <c r="B112" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A113" s="6">
+    <row r="113" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="5">
         <v>132925</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A114" s="6">
+    <row r="114" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="5">
         <v>132930</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A115" s="6">
+    <row r="115" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="5">
         <v>132960</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A116" s="6">
+    <row r="116" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="5">
         <v>132931</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B116" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A117" s="6">
+    <row r="117" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="5">
         <v>132932</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A118" s="6">
+    <row r="118" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="5">
         <v>132938</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A119" s="6">
+    <row r="119" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="5">
         <v>132933</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A120" s="6">
+    <row r="120" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="5">
         <v>132931</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="B120" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A121" s="6">
+    <row r="121" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="5">
         <v>132934</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A122" s="6">
+    <row r="122" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="5">
         <v>132960</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A123" s="6">
+    <row r="123" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="5">
         <v>132936</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="B123" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A124" s="6">
+    <row r="124" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="5">
         <v>132950</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B124" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A125" s="6">
+    <row r="125" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="5">
         <v>132953</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A126" s="6">
+    <row r="126" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="5">
         <v>132955</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A127" s="6">
+    <row r="127" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="5">
         <v>132962</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A128" s="6">
+    <row r="128" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="5">
         <v>132935</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B128" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A129" s="6">
+    <row r="129" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="5">
         <v>132924</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A130" s="6">
+    <row r="130" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="5">
         <v>132936</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A131" s="6">
+    <row r="131" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="5">
         <v>132935</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A132" s="6">
+    <row r="132" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="5">
         <v>132931</v>
       </c>
-      <c r="B132" s="7" t="s">
+      <c r="B132" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A133" s="6">
+    <row r="133" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="5">
         <v>132937</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A134" s="6">
+    <row r="134" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="5">
         <v>132938</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A135" s="6">
+    <row r="135" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="5">
         <v>132938</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A136" s="6">
+    <row r="136" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="5">
         <v>132939</v>
       </c>
-      <c r="B136" s="7" t="s">
+      <c r="B136" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A137" s="6">
+    <row r="137" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="5">
         <v>132942</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A138" s="6">
+    <row r="138" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="5">
         <v>132928</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A139" s="6">
+    <row r="139" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="5">
         <v>132937</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A140" s="6">
+    <row r="140" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="5">
         <v>132940</v>
       </c>
-      <c r="B140" s="7" t="s">
+      <c r="B140" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A141" s="6">
+    <row r="141" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="5">
         <v>132935</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A142" s="6">
+    <row r="142" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="5">
         <v>132941</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A143" s="6">
+    <row r="143" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="5">
         <v>132946</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A144" s="6">
+    <row r="144" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="5">
         <v>132962</v>
       </c>
-      <c r="B144" s="7" t="s">
+      <c r="B144" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A145" s="6">
+    <row r="145" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="5">
         <v>132942</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="6" t="s">
         <v>77</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A146" s="6">
+    <row r="146" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="5">
         <v>132929</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A147" s="6">
+    <row r="147" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="5">
         <v>132936</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A148" s="6">
+    <row r="148" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="5">
         <v>132926</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A149" s="6">
+    <row r="149" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="5">
         <v>132943</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A150" s="6">
+    <row r="150" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="5">
         <v>132944</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="6" t="s">
         <v>81</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A151" s="6">
+    <row r="151" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="5">
         <v>132946</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="B151" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A152" s="6">
+    <row r="152" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="5">
         <v>132962</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B152" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A153" s="6">
+    <row r="153" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="5">
         <v>132943</v>
       </c>
-      <c r="B153" s="7" t="s">
+      <c r="B153" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A154" s="6">
+    <row r="154" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="5">
         <v>132954</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A155" s="6">
+    <row r="155" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="5">
         <v>132952</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="B155" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A156" s="6">
+    <row r="156" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="5">
         <v>132961</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A157" s="6">
+    <row r="157" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="5">
         <v>132956</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A158" s="6">
+    <row r="158" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="5">
         <v>132926</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B158" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A159" s="6">
+    <row r="159" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="5">
         <v>132928</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B159" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A160" s="6">
+    <row r="160" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="5">
         <v>132945</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A161" s="6">
+    <row r="161" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="5">
         <v>132946</v>
       </c>
-      <c r="B161" s="7" t="s">
+      <c r="B161" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A162" s="6">
+    <row r="162" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="5">
         <v>132937</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A163" s="6">
+    <row r="163" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="5">
         <v>132946</v>
       </c>
-      <c r="B163" s="7" t="s">
+      <c r="B163" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A164" s="6">
+    <row r="164" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="5">
         <v>132947</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A165" s="6">
+    <row r="165" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="5">
         <v>132947</v>
       </c>
-      <c r="B165" s="7" t="s">
+      <c r="B165" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A166" s="6">
+    <row r="166" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="5">
         <v>132948</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="6" t="s">
         <v>87</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A167" s="6">
+    <row r="167" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="5">
         <v>132952</v>
       </c>
-      <c r="B167" s="7" t="s">
+      <c r="B167" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A168" s="6">
+    <row r="168" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="5">
         <v>132927</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A169" s="6">
+    <row r="169" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="5">
         <v>132931</v>
       </c>
-      <c r="B169" s="7" t="s">
+      <c r="B169" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A170" s="6">
+    <row r="170" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="5">
         <v>132928</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A171" s="6">
+    <row r="171" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="5">
         <v>132949</v>
       </c>
-      <c r="B171" s="7" t="s">
+      <c r="B171" s="6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A172" s="6">
+    <row r="172" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="5">
         <v>132950</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="B172" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A173" s="6">
+    <row r="173" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A173" s="5">
         <v>132951</v>
       </c>
-      <c r="B173" s="7" t="s">
+      <c r="B173" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A174" s="6">
+    <row r="174" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A174" s="5">
         <v>132926</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A175" s="6">
+    <row r="175" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="5">
         <v>132946</v>
       </c>
-      <c r="B175" s="7" t="s">
+      <c r="B175" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A176" s="6">
+    <row r="176" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="5">
         <v>132951</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A177" s="6">
+    <row r="177" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="5">
         <v>132952</v>
       </c>
-      <c r="B177" s="7" t="s">
+      <c r="B177" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A178" s="6">
+    <row r="178" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="5">
         <v>132953</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A179" s="6">
+    <row r="179" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="5">
         <v>132950</v>
       </c>
-      <c r="B179" s="7" t="s">
+      <c r="B179" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A180" s="6">
+    <row r="180" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="5">
         <v>132946</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="6" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A181" s="6">
+    <row r="181" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="5">
         <v>132954</v>
       </c>
-      <c r="B181" s="7" t="s">
+      <c r="B181" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A182" s="6">
+    <row r="182" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="5">
         <v>132955</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A183" s="6">
+    <row r="183" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="5">
         <v>132951</v>
       </c>
-      <c r="B183" s="7" t="s">
+      <c r="B183" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A184" s="6">
+    <row r="184" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="5">
         <v>132929</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="6" t="s">
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A185" s="6">
+    <row r="185" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="5">
         <v>132926</v>
       </c>
-      <c r="B185" s="7" t="s">
+      <c r="B185" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A186" s="6">
+    <row r="186" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="5">
         <v>132956</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B186" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A187" s="6">
+    <row r="187" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="5">
         <v>132954</v>
       </c>
-      <c r="B187" s="7" t="s">
+      <c r="B187" s="6" t="s">
         <v>82</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A188" s="6">
+    <row r="188" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="5">
         <v>132957</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A189" s="6">
+    <row r="189" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="5">
         <v>132958</v>
       </c>
-      <c r="B189" s="7" t="s">
+      <c r="B189" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A190" s="6">
+    <row r="190" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="5">
         <v>132928</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A191" s="6">
+    <row r="191" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A191" s="5">
         <v>132955</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A192" s="6">
+    <row r="192" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A192" s="5">
         <v>132959</v>
       </c>
-      <c r="B192" s="7" t="s">
+      <c r="B192" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A193" s="6">
+    <row r="193" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="5">
         <v>132959</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A194" s="6">
+    <row r="194" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="5">
         <v>132955</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A195" s="6">
+    <row r="195" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="5">
         <v>132960</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="6" t="s">
         <v>64</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A196" s="6">
+    <row r="196" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="5">
         <v>132961</v>
       </c>
-      <c r="B196" s="7" t="s">
+      <c r="B196" s="6" t="s">
         <v>83</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A197" s="6">
+    <row r="197" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="5">
         <v>132925</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="6" t="s">
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A198" s="6">
+    <row r="198" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="5">
         <v>132957</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="6" t="s">
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A199" s="6">
+    <row r="199" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A199" s="5">
         <v>132938</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="6" t="s">
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A200" s="6">
+    <row r="200" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="5">
         <v>132947</v>
       </c>
-      <c r="B200" s="7" t="s">
+      <c r="B200" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A201" s="6">
+    <row r="201" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="5">
         <v>132928</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="6" t="s">
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A202" s="6">
+    <row r="202" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A202" s="5">
         <v>132962</v>
       </c>
-      <c r="B202" s="7" t="s">
+      <c r="B202" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A203" s="6">
+    <row r="203" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A203" s="5">
         <v>132975</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A204" s="6">
+    <row r="204" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A204" s="5">
         <v>132964</v>
       </c>
-      <c r="B204" s="7" t="s">
+      <c r="B204" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A205" s="6">
+    <row r="205" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A205" s="5">
         <v>132964</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A206" s="6">
+    <row r="206" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A206" s="5">
         <v>132965</v>
       </c>
-      <c r="B206" s="7" t="s">
+      <c r="B206" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A207" s="6">
+    <row r="207" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="5">
         <v>132963</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="6" t="s">
         <v>96</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A208" s="6">
+    <row r="208" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="5">
         <v>132964</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A209" s="6">
+    <row r="209" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="5">
         <v>132996</v>
       </c>
-      <c r="B209" s="7" t="s">
+      <c r="B209" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A210" s="6">
+    <row r="210" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="5">
         <v>132966</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A211" s="6">
+    <row r="211" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="5">
         <v>132967</v>
       </c>
-      <c r="B211" s="7" t="s">
+      <c r="B211" s="6" t="s">
         <v>99</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A212" s="6">
+    <row r="212" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="5">
         <v>132999</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A213" s="6">
+    <row r="213" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A213" s="5">
         <v>132986</v>
       </c>
-      <c r="B213" s="7" t="s">
+      <c r="B213" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A214" s="6">
+    <row r="214" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="5">
         <v>132997</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A215" s="6">
+    <row r="215" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="5">
         <v>132968</v>
       </c>
-      <c r="B215" s="7" t="s">
+      <c r="B215" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A216" s="6">
+    <row r="216" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="5">
         <v>132969</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A217" s="6">
+    <row r="217" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="5">
         <v>132971</v>
       </c>
-      <c r="B217" s="7" t="s">
+      <c r="B217" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A218" s="6">
+    <row r="218" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="5">
         <v>132970</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A219" s="6">
+    <row r="219" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="5">
         <v>132991</v>
       </c>
-      <c r="B219" s="7" t="s">
+      <c r="B219" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A220" s="6">
+    <row r="220" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="5">
         <v>132988</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A221" s="6">
+    <row r="221" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="5">
         <v>132995</v>
       </c>
-      <c r="B221" s="7" t="s">
+      <c r="B221" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A222" s="6">
+    <row r="222" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="5">
         <v>132971</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A223" s="6">
+    <row r="223" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="5">
         <v>132975</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="B223" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="224" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A224" s="6">
+    <row r="224" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="5">
         <v>132972</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="225" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A225" s="6">
+    <row r="225" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="5">
         <v>132985</v>
       </c>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="226" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A226" s="6">
+    <row r="226" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="5">
         <v>132973</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="227" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A227" s="6">
+    <row r="227" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="5">
         <v>132998</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="228" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A228" s="6">
+    <row r="228" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="5">
         <v>132974</v>
       </c>
-      <c r="B228" s="7" t="s">
+      <c r="B228" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="229" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A229" s="6">
+    <row r="229" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="5">
         <v>132975</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="6" t="s">
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="230" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A230" s="6">
+    <row r="230" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="5">
         <v>132976</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B230" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="231" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A231" s="6">
+    <row r="231" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="5">
         <v>132999</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="232" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A232" s="6">
+    <row r="232" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="5">
         <v>132977</v>
       </c>
-      <c r="B232" s="7" t="s">
+      <c r="B232" s="6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="233" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A233" s="6">
+    <row r="233" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="5">
         <v>132976</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="234" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A234" s="6">
+    <row r="234" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="5">
         <v>132989</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="235" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A235" s="6">
+    <row r="235" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="5">
         <v>132996</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="236" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A236" s="6">
+    <row r="236" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="5">
         <v>132964</v>
       </c>
-      <c r="B236" s="7" t="s">
+      <c r="B236" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="237" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A237" s="6">
+    <row r="237" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="5">
         <v>132978</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="238" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A238" s="6">
+    <row r="238" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="5">
         <v>132979</v>
       </c>
-      <c r="B238" s="7" t="s">
+      <c r="B238" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="239" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A239" s="6">
+    <row r="239" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="5">
         <v>132981</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="240" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A240" s="6">
+    <row r="240" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="5">
         <v>132997</v>
       </c>
-      <c r="B240" s="7" t="s">
+      <c r="B240" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="241" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A241" s="6">
+    <row r="241" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="5">
         <v>132996</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="242" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A242" s="6">
+    <row r="242" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="5">
         <v>132994</v>
       </c>
-      <c r="B242" s="7" t="s">
+      <c r="B242" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="243" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A243" s="6">
+    <row r="243" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="5">
         <v>132971</v>
       </c>
-      <c r="B243" s="7" t="s">
+      <c r="B243" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="244" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A244" s="6">
+    <row r="244" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="5">
         <v>132980</v>
       </c>
-      <c r="B244" s="7" t="s">
+      <c r="B244" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="245" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A245" s="6">
+    <row r="245" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="5">
         <v>132981</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="6" t="s">
         <v>120</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="246" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A246" s="6">
+    <row r="246" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="5">
         <v>132964</v>
       </c>
-      <c r="B246" s="7" t="s">
+      <c r="B246" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="247" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A247" s="6">
+    <row r="247" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="5">
         <v>132997</v>
       </c>
-      <c r="B247" s="7" t="s">
+      <c r="B247" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="248" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A248" s="6">
+    <row r="248" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="5">
         <v>132982</v>
       </c>
-      <c r="B248" s="7" t="s">
+      <c r="B248" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="249" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A249" s="6">
+    <row r="249" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="5">
         <v>132993</v>
       </c>
-      <c r="B249" s="7" t="s">
+      <c r="B249" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="250" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A250" s="6">
+    <row r="250" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="5">
         <v>132984</v>
       </c>
-      <c r="B250" s="7" t="s">
+      <c r="B250" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="251" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A251" s="6">
+    <row r="251" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="5">
         <v>132978</v>
       </c>
-      <c r="B251" s="7" t="s">
+      <c r="B251" s="6" t="s">
         <v>118</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="252" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A252" s="6">
+    <row r="252" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="5">
         <v>132992</v>
       </c>
-      <c r="B252" s="7" t="s">
+      <c r="B252" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="253" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A253" s="6">
+    <row r="253" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="5">
         <v>132999</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="254" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A254" s="6">
+    <row r="254" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="5">
         <v>132983</v>
       </c>
-      <c r="B254" s="7" t="s">
+      <c r="B254" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="255" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A255" s="6">
+    <row r="255" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="5">
         <v>133003</v>
       </c>
-      <c r="B255" s="7" t="s">
+      <c r="B255" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="256" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A256" s="6">
+    <row r="256" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="5">
         <v>132980</v>
       </c>
-      <c r="B256" s="7" t="s">
+      <c r="B256" s="6" t="s">
         <v>122</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="257" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A257" s="6">
+    <row r="257" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="5">
         <v>132983</v>
       </c>
-      <c r="B257" s="7" t="s">
+      <c r="B257" s="6" t="s">
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="258" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A258" s="6">
+    <row r="258" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="5">
         <v>132997</v>
       </c>
-      <c r="B258" s="7" t="s">
+      <c r="B258" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="259" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A259" s="6">
+    <row r="259" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="5">
         <v>132999</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B259" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="260" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A260" s="6">
+    <row r="260" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="5">
         <v>132985</v>
       </c>
-      <c r="B260" s="7" t="s">
+      <c r="B260" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="261" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A261" s="6">
+    <row r="261" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="5">
         <v>132999</v>
       </c>
-      <c r="B261" s="7" t="s">
+      <c r="B261" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="262" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A262" s="6">
+    <row r="262" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="5">
         <v>132972</v>
       </c>
-      <c r="B262" s="7" t="s">
+      <c r="B262" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="263" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A263" s="6">
+    <row r="263" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="5">
         <v>132984</v>
       </c>
-      <c r="B263" s="7" t="s">
+      <c r="B263" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="264" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A264" s="6">
+    <row r="264" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="5">
         <v>132984</v>
       </c>
-      <c r="B264" s="7" t="s">
+      <c r="B264" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="265" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A265" s="6">
+    <row r="265" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="5">
         <v>132999</v>
       </c>
-      <c r="B265" s="7" t="s">
+      <c r="B265" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="266" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A266" s="6">
+    <row r="266" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="5">
         <v>132969</v>
       </c>
-      <c r="B266" s="7" t="s">
+      <c r="B266" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="267" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A267" s="6">
+    <row r="267" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="5">
         <v>132986</v>
       </c>
-      <c r="B267" s="7" t="s">
+      <c r="B267" s="6" t="s">
         <v>101</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="268" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A268" s="6">
+    <row r="268" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="5">
         <v>132982</v>
       </c>
-      <c r="B268" s="7" t="s">
+      <c r="B268" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="269" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A269" s="6">
+    <row r="269" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="5">
         <v>132971</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="B269" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="270" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A270" s="6">
+    <row r="270" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="5">
         <v>132987</v>
       </c>
-      <c r="B270" s="7" t="s">
+      <c r="B270" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="271" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A271" s="6">
+    <row r="271" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="5">
         <v>132964</v>
       </c>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="272" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A272" s="6">
+    <row r="272" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="5">
         <v>132973</v>
       </c>
-      <c r="B272" s="7" t="s">
+      <c r="B272" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="273" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A273" s="6">
+    <row r="273" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="5">
         <v>132971</v>
       </c>
-      <c r="B273" s="7" t="s">
+      <c r="B273" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="274" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A274" s="6">
+    <row r="274" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="5">
         <v>132970</v>
       </c>
-      <c r="B274" s="7" t="s">
+      <c r="B274" s="6" t="s">
         <v>106</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="275" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A275" s="6">
+    <row r="275" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="5">
         <v>132997</v>
       </c>
-      <c r="B275" s="7" t="s">
+      <c r="B275" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="276" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A276" s="6">
+    <row r="276" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="5">
         <v>133006</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="277" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A277" s="6">
+    <row r="277" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="5">
         <v>132969</v>
       </c>
-      <c r="B277" s="7" t="s">
+      <c r="B277" s="6" t="s">
         <v>104</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="278" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A278" s="6">
+    <row r="278" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="5">
         <v>133000</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="B278" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="279" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A279" s="6">
+    <row r="279" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="5">
         <v>132988</v>
       </c>
-      <c r="B279" s="7" t="s">
+      <c r="B279" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="280" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A280" s="6">
+    <row r="280" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="5">
         <v>132989</v>
       </c>
-      <c r="B280" s="7" t="s">
+      <c r="B280" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="281" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A281" s="6">
+    <row r="281" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="5">
         <v>132990</v>
       </c>
-      <c r="B281" s="7" t="s">
+      <c r="B281" s="6" t="s">
         <v>132</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="282" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A282" s="6">
+    <row r="282" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="5">
         <v>132972</v>
       </c>
-      <c r="B282" s="7" t="s">
+      <c r="B282" s="6" t="s">
         <v>110</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="283" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A283" s="6">
+    <row r="283" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="5">
         <v>132991</v>
       </c>
-      <c r="B283" s="7" t="s">
+      <c r="B283" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="284" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A284" s="6">
+    <row r="284" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="5">
         <v>132992</v>
       </c>
-      <c r="B284" s="7" t="s">
+      <c r="B284" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="285" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A285" s="6">
+    <row r="285" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="5">
         <v>132993</v>
       </c>
-      <c r="B285" s="7" t="s">
+      <c r="B285" s="6" t="s">
         <v>124</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="286" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A286" s="6">
+    <row r="286" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="5">
         <v>132994</v>
       </c>
-      <c r="B286" s="7" t="s">
+      <c r="B286" s="6" t="s">
         <v>121</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="287" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A287" s="6">
+    <row r="287" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="5">
         <v>132979</v>
       </c>
-      <c r="B287" s="7" t="s">
+      <c r="B287" s="6" t="s">
         <v>119</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="288" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A288" s="6">
+    <row r="288" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="5">
         <v>132995</v>
       </c>
-      <c r="B288" s="7" t="s">
+      <c r="B288" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="289" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A289" s="6">
+    <row r="289" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A289" s="5">
         <v>132964</v>
       </c>
-      <c r="B289" s="7" t="s">
+      <c r="B289" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="290" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A290" s="6">
+    <row r="290" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="5">
         <v>132996</v>
       </c>
-      <c r="B290" s="7" t="s">
+      <c r="B290" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="291" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A291" s="6">
+    <row r="291" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A291" s="5">
         <v>132997</v>
       </c>
-      <c r="B291" s="7" t="s">
+      <c r="B291" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="292" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A292" s="6">
+    <row r="292" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="5">
         <v>132971</v>
       </c>
-      <c r="B292" s="7" t="s">
+      <c r="B292" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="293" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A293" s="6">
+    <row r="293" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A293" s="5">
         <v>132992</v>
       </c>
-      <c r="B293" s="7" t="s">
+      <c r="B293" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="294" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A294" s="6">
+    <row r="294" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A294" s="5">
         <v>132976</v>
       </c>
-      <c r="B294" s="7" t="s">
+      <c r="B294" s="6" t="s">
         <v>115</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="295" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A295" s="6">
+    <row r="295" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A295" s="5">
         <v>132998</v>
       </c>
-      <c r="B295" s="7" t="s">
+      <c r="B295" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="296" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A296" s="6">
+    <row r="296" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A296" s="5">
         <v>132999</v>
       </c>
-      <c r="B296" s="7" t="s">
+      <c r="B296" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="297" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A297" s="6">
+    <row r="297" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="5">
         <v>133000</v>
       </c>
-      <c r="B297" s="7" t="s">
+      <c r="B297" s="6" t="s">
         <v>131</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="298" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A298" s="6">
+    <row r="298" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="5">
         <v>132989</v>
       </c>
-      <c r="B298" s="7" t="s">
+      <c r="B298" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="299" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A299" s="6">
+    <row r="299" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="5">
         <v>132964</v>
       </c>
-      <c r="B299" s="7" t="s">
+      <c r="B299" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="300" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A300" s="6">
+    <row r="300" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A300" s="5">
         <v>133001</v>
       </c>
-      <c r="B300" s="7" t="s">
+      <c r="B300" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="301" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A301" s="6">
+    <row r="301" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="5">
         <v>133002</v>
       </c>
-      <c r="B301" s="7" t="s">
+      <c r="B301" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="302" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A302" s="6">
+    <row r="302" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="5">
         <v>133003</v>
       </c>
-      <c r="B302" s="7" t="s">
+      <c r="B302" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="303" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A303" s="6">
+    <row r="303" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="5">
         <v>132996</v>
       </c>
-      <c r="B303" s="7" t="s">
+      <c r="B303" s="6" t="s">
         <v>97</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="304" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A304" s="6">
+    <row r="304" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="5">
         <v>132971</v>
       </c>
-      <c r="B304" s="7" t="s">
+      <c r="B304" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="305" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A305" s="6">
+    <row r="305" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A305" s="5">
         <v>132973</v>
       </c>
-      <c r="B305" s="7" t="s">
+      <c r="B305" s="6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="306" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A306" s="6">
+    <row r="306" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="5">
         <v>132965</v>
       </c>
-      <c r="B306" s="7" t="s">
+      <c r="B306" s="6" t="s">
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="307" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A307" s="6">
+    <row r="307" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="5">
         <v>133003</v>
       </c>
-      <c r="B307" s="7" t="s">
+      <c r="B307" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="308" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A308" s="6">
+    <row r="308" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="5">
         <v>133004</v>
       </c>
-      <c r="B308" s="7" t="s">
+      <c r="B308" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="309" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A309" s="6">
+    <row r="309" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="5">
         <v>132999</v>
       </c>
-      <c r="B309" s="7" t="s">
+      <c r="B309" s="6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="310" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A310" s="6">
+    <row r="310" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A310" s="5">
         <v>133005</v>
       </c>
-      <c r="B310" s="7" t="s">
+      <c r="B310" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="311" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A311" s="6">
+    <row r="311" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="5">
         <v>132964</v>
       </c>
-      <c r="B311" s="7" t="s">
+      <c r="B311" s="6" t="s">
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="312" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A312" s="6">
+    <row r="312" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A312" s="5">
         <v>133006</v>
       </c>
-      <c r="B312" s="7" t="s">
+      <c r="B312" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="313" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A313" s="6">
+    <row r="313" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A313" s="5">
         <v>132992</v>
       </c>
-      <c r="B313" s="7" t="s">
+      <c r="B313" s="6" t="s">
         <v>126</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="314" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A314" s="6">
+    <row r="314" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A314" s="5">
         <v>133008</v>
       </c>
-      <c r="B314" s="7" t="s">
+      <c r="B314" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="315" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A315" s="6">
+    <row r="315" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A315" s="5">
         <v>133028</v>
       </c>
-      <c r="B315" s="7" t="s">
+      <c r="B315" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="316" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A316" s="6">
+    <row r="316" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A316" s="5">
         <v>133014</v>
       </c>
-      <c r="B316" s="7" t="s">
+      <c r="B316" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="317" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A317" s="6">
+    <row r="317" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A317" s="5">
         <v>133009</v>
       </c>
-      <c r="B317" s="7" t="s">
+      <c r="B317" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="318" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A318" s="6">
+    <row r="318" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A318" s="5">
         <v>133008</v>
       </c>
-      <c r="B318" s="7" t="s">
+      <c r="B318" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="319" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A319" s="6">
+    <row r="319" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A319" s="5">
         <v>133010</v>
       </c>
-      <c r="B319" s="7" t="s">
+      <c r="B319" s="6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="320" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A320" s="6">
+    <row r="320" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A320" s="5">
         <v>133011</v>
       </c>
-      <c r="B320" s="7" t="s">
+      <c r="B320" s="6" t="s">
         <v>142</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="321" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A321" s="6">
+    <row r="321" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A321" s="5">
         <v>133012</v>
       </c>
-      <c r="B321" s="7" t="s">
+      <c r="B321" s="6" t="s">
         <v>143</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="322" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A322" s="6">
+    <row r="322" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A322" s="5">
         <v>133013</v>
       </c>
-      <c r="B322" s="7" t="s">
+      <c r="B322" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="323" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A323" s="6">
+    <row r="323" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A323" s="5">
         <v>133042</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B323" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="324" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A324" s="6">
+    <row r="324" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A324" s="5">
         <v>133014</v>
       </c>
-      <c r="B324" s="7" t="s">
+      <c r="B324" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="325" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A325" s="6">
+    <row r="325" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A325" s="5">
         <v>133064</v>
       </c>
-      <c r="B325" s="7" t="s">
+      <c r="B325" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="326" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A326" s="6">
+    <row r="326" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A326" s="5">
         <v>133015</v>
       </c>
-      <c r="B326" s="7" t="s">
+      <c r="B326" s="6" t="s">
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="327" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A327" s="6">
+    <row r="327" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A327" s="5">
         <v>133016</v>
       </c>
-      <c r="B327" s="7" t="s">
+      <c r="B327" s="6" t="s">
         <v>148</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="328" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A328" s="6">
+    <row r="328" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A328" s="5">
         <v>133058</v>
       </c>
-      <c r="B328" s="7" t="s">
+      <c r="B328" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="329" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A329" s="6">
+    <row r="329" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A329" s="5">
         <v>133017</v>
       </c>
-      <c r="B329" s="7" t="s">
+      <c r="B329" s="6" t="s">
         <v>150</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="330" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A330" s="6">
+    <row r="330" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A330" s="5">
         <v>133020</v>
       </c>
-      <c r="B330" s="7" t="s">
+      <c r="B330" s="6" t="s">
         <v>151</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="331" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A331" s="6">
+    <row r="331" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A331" s="5">
         <v>133018</v>
       </c>
-      <c r="B331" s="7" t="s">
+      <c r="B331" s="6" t="s">
         <v>152</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="332" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A332" s="6">
+    <row r="332" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A332" s="5">
         <v>133019</v>
       </c>
-      <c r="B332" s="7" t="s">
+      <c r="B332" s="6" t="s">
         <v>153</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="333" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A333" s="6">
+    <row r="333" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A333" s="5">
         <v>133069</v>
       </c>
-      <c r="B333" s="7" t="s">
+      <c r="B333" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="334" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A334" s="6">
+    <row r="334" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A334" s="5">
         <v>133021</v>
       </c>
-      <c r="B334" s="7" t="s">
+      <c r="B334" s="6" t="s">
         <v>155</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="335" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A335" s="6">
+    <row r="335" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A335" s="5">
         <v>133023</v>
       </c>
-      <c r="B335" s="7" t="s">
+      <c r="B335" s="6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="336" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A336" s="6">
+    <row r="336" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A336" s="5">
         <v>133022</v>
       </c>
-      <c r="B336" s="7" t="s">
+      <c r="B336" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="337" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A337" s="6">
+    <row r="337" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A337" s="5">
         <v>133024</v>
       </c>
-      <c r="B337" s="7" t="s">
+      <c r="B337" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="338" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A338" s="6">
+    <row r="338" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A338" s="5">
         <v>133023</v>
       </c>
-      <c r="B338" s="7" t="s">
+      <c r="B338" s="6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="339" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A339" s="6">
+    <row r="339" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A339" s="5">
         <v>133025</v>
       </c>
-      <c r="B339" s="7" t="s">
+      <c r="B339" s="6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="340" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A340" s="6">
+    <row r="340" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A340" s="5">
         <v>133014</v>
       </c>
-      <c r="B340" s="7" t="s">
+      <c r="B340" s="6" t="s">
         <v>139</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="341" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A341" s="6">
+    <row r="341" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A341" s="5">
         <v>133062</v>
       </c>
-      <c r="B341" s="7" t="s">
+      <c r="B341" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="342" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A342" s="6">
+    <row r="342" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A342" s="5">
         <v>133031</v>
       </c>
-      <c r="B342" s="7" t="s">
+      <c r="B342" s="6" t="s">
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="343" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A343" s="6">
+    <row r="343" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A343" s="5">
         <v>133026</v>
       </c>
-      <c r="B343" s="7" t="s">
+      <c r="B343" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="344" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A344" s="6">
+    <row r="344" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A344" s="5">
         <v>133027</v>
       </c>
-      <c r="B344" s="7" t="s">
+      <c r="B344" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="345" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A345" s="6">
+    <row r="345" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A345" s="5">
         <v>133028</v>
       </c>
-      <c r="B345" s="7" t="s">
+      <c r="B345" s="6" t="s">
         <v>138</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="346" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A346" s="6">
+    <row r="346" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A346" s="5">
         <v>133029</v>
       </c>
-      <c r="B346" s="7" t="s">
+      <c r="B346" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="347" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A347" s="6">
+    <row r="347" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A347" s="5">
         <v>133030</v>
       </c>
-      <c r="B347" s="7" t="s">
+      <c r="B347" s="6" t="s">
         <v>164</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="348" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A348" s="6">
+    <row r="348" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A348" s="5">
         <v>133031</v>
       </c>
-      <c r="B348" s="7" t="s">
+      <c r="B348" s="6" t="s">
         <v>161</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="349" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A349" s="6">
+    <row r="349" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A349" s="5">
         <v>133032</v>
       </c>
-      <c r="B349" s="7" t="s">
+      <c r="B349" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="350" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A350" s="6">
+    <row r="350" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A350" s="5">
         <v>133033</v>
       </c>
-      <c r="B350" s="7" t="s">
+      <c r="B350" s="6" t="s">
         <v>166</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="351" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A351" s="6">
+    <row r="351" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A351" s="5">
         <v>133037</v>
       </c>
-      <c r="B351" s="7" t="s">
+      <c r="B351" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="352" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A352" s="6">
+    <row r="352" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A352" s="5">
         <v>133034</v>
       </c>
-      <c r="B352" s="7" t="s">
+      <c r="B352" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="353" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A353" s="6">
+    <row r="353" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A353" s="5">
         <v>133067</v>
       </c>
-      <c r="B353" s="7" t="s">
+      <c r="B353" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="354" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A354" s="6">
+    <row r="354" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A354" s="5">
         <v>133035</v>
       </c>
-      <c r="B354" s="7" t="s">
+      <c r="B354" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="355" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A355" s="6">
+    <row r="355" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A355" s="5">
         <v>133038</v>
       </c>
-      <c r="B355" s="7" t="s">
+      <c r="B355" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="356" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A356" s="6">
+    <row r="356" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A356" s="5">
         <v>133036</v>
       </c>
-      <c r="B356" s="7" t="s">
+      <c r="B356" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="357" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A357" s="6">
+    <row r="357" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A357" s="5">
         <v>133037</v>
       </c>
-      <c r="B357" s="7" t="s">
+      <c r="B357" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="358" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A358" s="6">
+    <row r="358" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A358" s="5">
         <v>133017</v>
       </c>
-      <c r="B358" s="7" t="s">
+      <c r="B358" s="6" t="s">
         <v>150</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="359" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A359" s="6">
+    <row r="359" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A359" s="5">
         <v>133022</v>
       </c>
-      <c r="B359" s="7" t="s">
+      <c r="B359" s="6" t="s">
         <v>157</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="360" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A360" s="6">
+    <row r="360" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A360" s="5">
         <v>133038</v>
       </c>
-      <c r="B360" s="7" t="s">
+      <c r="B360" s="6" t="s">
         <v>171</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="361" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A361" s="6">
+    <row r="361" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A361" s="5">
         <v>133039</v>
       </c>
-      <c r="B361" s="7" t="s">
+      <c r="B361" s="6" t="s">
         <v>173</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="362" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A362" s="6">
+    <row r="362" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A362" s="5">
         <v>133010</v>
       </c>
-      <c r="B362" s="7" t="s">
+      <c r="B362" s="6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="363" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A363" s="6">
+    <row r="363" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A363" s="5">
         <v>133040</v>
       </c>
-      <c r="B363" s="7" t="s">
+      <c r="B363" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="364" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A364" s="6">
+    <row r="364" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A364" s="5">
         <v>133051</v>
       </c>
-      <c r="B364" s="7" t="s">
+      <c r="B364" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="365" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A365" s="6">
+    <row r="365" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A365" s="5">
         <v>133041</v>
       </c>
-      <c r="B365" s="7" t="s">
+      <c r="B365" s="6" t="s">
         <v>176</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="366" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A366" s="6">
+    <row r="366" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A366" s="5">
         <v>133071</v>
       </c>
-      <c r="B366" s="7" t="s">
+      <c r="B366" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="367" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A367" s="6">
+    <row r="367" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A367" s="5">
         <v>133042</v>
       </c>
-      <c r="B367" s="7" t="s">
+      <c r="B367" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="368" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A368" s="6">
+    <row r="368" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A368" s="5">
         <v>133042</v>
       </c>
-      <c r="B368" s="7" t="s">
+      <c r="B368" s="6" t="s">
         <v>145</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="369" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A369" s="6">
+    <row r="369" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A369" s="5">
         <v>133043</v>
       </c>
-      <c r="B369" s="7" t="s">
+      <c r="B369" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="370" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A370" s="6">
+    <row r="370" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A370" s="5">
         <v>133044</v>
       </c>
-      <c r="B370" s="7" t="s">
+      <c r="B370" s="6" t="s">
         <v>179</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="371" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A371" s="6">
+    <row r="371" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A371" s="5">
         <v>133045</v>
       </c>
-      <c r="B371" s="7" t="s">
+      <c r="B371" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="372" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A372" s="6">
+    <row r="372" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A372" s="5">
         <v>133057</v>
       </c>
-      <c r="B372" s="7" t="s">
+      <c r="B372" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="373" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A373" s="6">
+    <row r="373" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A373" s="5">
         <v>133048</v>
       </c>
-      <c r="B373" s="7" t="s">
+      <c r="B373" s="6" t="s">
         <v>181</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="374" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A374" s="6">
+    <row r="374" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A374" s="5">
         <v>133046</v>
       </c>
-      <c r="B374" s="7" t="s">
+      <c r="B374" s="6" t="s">
         <v>182</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="375" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A375" s="6">
+    <row r="375" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A375" s="5">
         <v>133047</v>
       </c>
-      <c r="B375" s="7" t="s">
+      <c r="B375" s="6" t="s">
         <v>183</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="376" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A376" s="6">
+    <row r="376" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A376" s="5">
         <v>133049</v>
       </c>
-      <c r="B376" s="7" t="s">
+      <c r="B376" s="6" t="s">
         <v>184</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="377" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A377" s="6">
+    <row r="377" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A377" s="5">
         <v>133050</v>
       </c>
-      <c r="B377" s="7" t="s">
+      <c r="B377" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="378" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A378" s="6">
+    <row r="378" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A378" s="5">
         <v>133051</v>
       </c>
-      <c r="B378" s="7" t="s">
+      <c r="B378" s="6" t="s">
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="379" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A379" s="6">
+    <row r="379" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A379" s="5">
         <v>133008</v>
       </c>
-      <c r="B379" s="7" t="s">
+      <c r="B379" s="6" t="s">
         <v>137</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="380" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A380" s="6">
+    <row r="380" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A380" s="5">
         <v>133047</v>
       </c>
-      <c r="B380" s="7" t="s">
+      <c r="B380" s="6" t="s">
         <v>183</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="381" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A381" s="6">
+    <row r="381" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A381" s="5">
         <v>133052</v>
       </c>
-      <c r="B381" s="7" t="s">
+      <c r="B381" s="6" t="s">
         <v>186</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="382" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A382" s="6">
+    <row r="382" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="5">
         <v>133032</v>
       </c>
-      <c r="B382" s="7" t="s">
+      <c r="B382" s="6" t="s">
         <v>165</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="383" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A383" s="6">
+    <row r="383" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="5">
         <v>133054</v>
       </c>
-      <c r="B383" s="7" t="s">
+      <c r="B383" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="384" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A384" s="6">
+    <row r="384" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="5">
         <v>133055</v>
       </c>
-      <c r="B384" s="7" t="s">
+      <c r="B384" s="6" t="s">
         <v>188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="385" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A385" s="6">
+    <row r="385" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="5">
         <v>133043</v>
       </c>
-      <c r="B385" s="7" t="s">
+      <c r="B385" s="6" t="s">
         <v>178</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="386" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A386" s="6">
+    <row r="386" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="5">
         <v>133034</v>
       </c>
-      <c r="B386" s="7" t="s">
+      <c r="B386" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="387" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A387" s="6">
+    <row r="387" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="5">
         <v>133057</v>
       </c>
-      <c r="B387" s="7" t="s">
+      <c r="B387" s="6" t="s">
         <v>180</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="388" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A388" s="6">
+    <row r="388" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="5">
         <v>133072</v>
       </c>
-      <c r="B388" s="7" t="s">
+      <c r="B388" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="389" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A389" s="6">
+    <row r="389" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="5">
         <v>133056</v>
       </c>
-      <c r="B389" s="7" t="s">
+      <c r="B389" s="6" t="s">
         <v>189</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="390" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A390" s="6">
+    <row r="390" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="5">
         <v>133058</v>
       </c>
-      <c r="B390" s="7" t="s">
+      <c r="B390" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="391" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A391" s="6">
+    <row r="391" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="5">
         <v>133045</v>
       </c>
-      <c r="B391" s="7" t="s">
+      <c r="B391" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="392" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A392" s="6">
+    <row r="392" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="5">
         <v>133059</v>
       </c>
-      <c r="B392" s="7" t="s">
+      <c r="B392" s="6" t="s">
         <v>190</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="393" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A393" s="6">
+    <row r="393" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="5">
         <v>133060</v>
       </c>
-      <c r="B393" s="7" t="s">
+      <c r="B393" s="6" t="s">
         <v>191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="394" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A394" s="6">
+    <row r="394" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="5">
         <v>133061</v>
       </c>
-      <c r="B394" s="7" t="s">
+      <c r="B394" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="395" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A395" s="6">
+    <row r="395" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="5">
         <v>133009</v>
       </c>
-      <c r="B395" s="7" t="s">
+      <c r="B395" s="6" t="s">
         <v>140</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="396" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A396" s="6">
+    <row r="396" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="5">
         <v>133062</v>
       </c>
-      <c r="B396" s="7" t="s">
+      <c r="B396" s="6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="397" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A397" s="6">
+    <row r="397" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="5">
         <v>133063</v>
       </c>
-      <c r="B397" s="7" t="s">
+      <c r="B397" s="6" t="s">
         <v>193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="398" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A398" s="6">
+    <row r="398" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="5">
         <v>133064</v>
       </c>
-      <c r="B398" s="7" t="s">
+      <c r="B398" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="399" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A399" s="6">
+    <row r="399" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="5">
         <v>133065</v>
       </c>
-      <c r="B399" s="7" t="s">
+      <c r="B399" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="400" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A400" s="6">
+    <row r="400" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="5">
         <v>133066</v>
       </c>
-      <c r="B400" s="7" t="s">
+      <c r="B400" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="401" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A401" s="6">
+    <row r="401" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="5">
         <v>133067</v>
       </c>
-      <c r="B401" s="7" t="s">
+      <c r="B401" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="402" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A402" s="6">
+    <row r="402" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="5">
         <v>133068</v>
       </c>
-      <c r="B402" s="7" t="s">
+      <c r="B402" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="403" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A403" s="6">
+    <row r="403" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="5">
         <v>133069</v>
       </c>
-      <c r="B403" s="7" t="s">
+      <c r="B403" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="404" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A404" s="6">
+    <row r="404" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="5">
         <v>133070</v>
       </c>
-      <c r="B404" s="7" t="s">
+      <c r="B404" s="6" t="s">
         <v>197</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="405" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A405" s="6">
+    <row r="405" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="5">
         <v>133034</v>
       </c>
-      <c r="B405" s="7" t="s">
+      <c r="B405" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="406" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A406" s="6">
+    <row r="406" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="5">
         <v>133040</v>
       </c>
-      <c r="B406" s="7" t="s">
+      <c r="B406" s="6" t="s">
         <v>174</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="407" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A407" s="6">
+    <row r="407" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="5">
         <v>133071</v>
       </c>
-      <c r="B407" s="7" t="s">
+      <c r="B407" s="6" t="s">
         <v>177</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="408" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A408" s="6">
+    <row r="408" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="5">
         <v>133072</v>
       </c>
-      <c r="B408" s="7" t="s">
+      <c r="B408" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="409" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A409" s="6">
+    <row r="409" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="5">
         <v>133050</v>
       </c>
-      <c r="B409" s="7" t="s">
+      <c r="B409" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="410" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A410" s="6">
+    <row r="410" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="5">
         <v>133073</v>
       </c>
-      <c r="B410" s="7" t="s">
+      <c r="B410" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="411" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A411" s="8">
+    <row r="411" spans="1:2" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A411" s="7">
         <v>133074</v>
       </c>
-      <c r="B411" s="9" t="s">
+      <c r="B411" s="8" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A412" s="9">
+        <v>98362</v>
+      </c>
+      <c r="B412" s="10" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A413" s="11">
+        <v>98353</v>
+      </c>
+      <c r="B413" s="12" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A414" s="11">
+        <v>98352</v>
+      </c>
+      <c r="B414" s="12" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A415" s="11">
+        <v>98354</v>
+      </c>
+      <c r="B415" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="11">
+        <v>98360</v>
+      </c>
+      <c r="B416" s="12" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A417" s="11">
+        <v>98356</v>
+      </c>
+      <c r="B417" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A418" s="11">
+        <v>98358</v>
+      </c>
+      <c r="B418" s="12" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A419" s="11">
+        <v>98355</v>
+      </c>
+      <c r="B419" s="12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A420" s="11">
+        <v>98361</v>
+      </c>
+      <c r="B420" s="12" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A421" s="11">
+        <v>98359</v>
+      </c>
+      <c r="B421" s="12" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A422" s="11">
+        <v>98357</v>
+      </c>
+      <c r="B422" s="12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A423" s="11">
+        <v>98379</v>
+      </c>
+      <c r="B423" s="12" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="11">
+        <v>98385</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A425" s="11">
+        <v>98380</v>
+      </c>
+      <c r="B425" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A426" s="11">
+        <v>98386</v>
+      </c>
+      <c r="B426" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A427" s="11">
+        <v>98375</v>
+      </c>
+      <c r="B427" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A428" s="11">
+        <v>98384</v>
+      </c>
+      <c r="B428" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A429" s="11">
+        <v>98389</v>
+      </c>
+      <c r="B429" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="11">
+        <v>98376</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A431" s="11">
+        <v>98381</v>
+      </c>
+      <c r="B431" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A432" s="11">
+        <v>98382</v>
+      </c>
+      <c r="B432" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A433" s="11">
+        <v>98390</v>
+      </c>
+      <c r="B433" s="12" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A434" s="11">
+        <v>98373</v>
+      </c>
+      <c r="B434" s="12" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A435" s="11">
+        <v>98388</v>
+      </c>
+      <c r="B435" s="12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A436" s="11">
+        <v>98383</v>
+      </c>
+      <c r="B436" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A437" s="11">
+        <v>98387</v>
+      </c>
+      <c r="B437" s="12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A438" s="11">
+        <v>98454</v>
+      </c>
+      <c r="B438" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A439" s="11">
+        <v>98461</v>
+      </c>
+      <c r="B439" s="12" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A440" s="11">
+        <v>98462</v>
+      </c>
+      <c r="B440" s="12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A441" s="11">
+        <v>98465</v>
+      </c>
+      <c r="B441" s="12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A442" s="11">
+        <v>98464</v>
+      </c>
+      <c r="B442" s="12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A443" s="11">
+        <v>98460</v>
+      </c>
+      <c r="B443" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A444" s="11">
+        <v>98459</v>
+      </c>
+      <c r="B444" s="12" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A445" s="11">
+        <v>98458</v>
+      </c>
+      <c r="B445" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A446" s="11">
+        <v>98455</v>
+      </c>
+      <c r="B446" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A447" s="11">
+        <v>98463</v>
+      </c>
+      <c r="B447" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A448" s="11">
+        <v>98467</v>
+      </c>
+      <c r="B448" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A449" s="11">
+        <v>98452</v>
+      </c>
+      <c r="B449" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A450" s="11">
+        <v>98466</v>
+      </c>
+      <c r="B450" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A451" s="11">
+        <v>98456</v>
+      </c>
+      <c r="B451" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A452" s="11">
+        <v>98457</v>
+      </c>
+      <c r="B452" s="12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A453" s="11">
+        <v>98453</v>
+      </c>
+      <c r="B453" s="12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A454" s="11">
+        <v>98320</v>
+      </c>
+      <c r="B454" s="12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A455" s="11">
+        <v>98321</v>
+      </c>
+      <c r="B455" s="12" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A456" s="11">
+        <v>98323</v>
+      </c>
+      <c r="B456" s="12" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A457" s="11">
+        <v>98326</v>
+      </c>
+      <c r="B457" s="12" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A458" s="11">
+        <v>98325</v>
+      </c>
+      <c r="B458" s="12" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A459" s="11">
+        <v>98324</v>
+      </c>
+      <c r="B459" s="12" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A460" s="11">
+        <v>98322</v>
+      </c>
+      <c r="B460" s="12" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A461" s="11">
+        <v>98402</v>
+      </c>
+      <c r="B461" s="12" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A462" s="11">
+        <v>98405</v>
+      </c>
+      <c r="B462" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A463" s="11">
+        <v>98397</v>
+      </c>
+      <c r="B463" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A464" s="11">
+        <v>98399</v>
+      </c>
+      <c r="B464" s="12" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A465" s="11">
+        <v>98395</v>
+      </c>
+      <c r="B465" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A466" s="11">
+        <v>98406</v>
+      </c>
+      <c r="B466" s="12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A467" s="11">
+        <v>98403</v>
+      </c>
+      <c r="B467" s="12" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A468" s="11">
+        <v>98404</v>
+      </c>
+      <c r="B468" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A469" s="11">
+        <v>98392</v>
+      </c>
+      <c r="B469" s="12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A470" s="11">
+        <v>98401</v>
+      </c>
+      <c r="B470" s="12" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A471" s="11">
+        <v>98400</v>
+      </c>
+      <c r="B471" s="12" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A472" s="11">
+        <v>98393</v>
+      </c>
+      <c r="B472" s="12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A473" s="11">
+        <v>98391</v>
+      </c>
+      <c r="B473" s="12" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A474" s="11">
+        <v>98396</v>
+      </c>
+      <c r="B474" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A475" s="11">
+        <v>98394</v>
+      </c>
+      <c r="B475" s="12" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A476" s="11">
+        <v>98398</v>
+      </c>
+      <c r="B476" s="12" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A477" s="11">
+        <v>98332</v>
+      </c>
+      <c r="B477" s="12" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A478" s="11">
+        <v>98327</v>
+      </c>
+      <c r="B478" s="12" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A479" s="11">
+        <v>98328</v>
+      </c>
+      <c r="B479" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A480" s="11">
+        <v>98335</v>
+      </c>
+      <c r="B480" s="12" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A481" s="11">
+        <v>98338</v>
+      </c>
+      <c r="B481" s="12" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A482" s="11">
+        <v>98331</v>
+      </c>
+      <c r="B482" s="12" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A483" s="11">
+        <v>98336</v>
+      </c>
+      <c r="B483" s="12" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A484" s="11">
+        <v>98339</v>
+      </c>
+      <c r="B484" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A485" s="11">
+        <v>98329</v>
+      </c>
+      <c r="B485" s="12" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A486" s="11">
+        <v>98341</v>
+      </c>
+      <c r="B486" s="12" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A487" s="11">
+        <v>98340</v>
+      </c>
+      <c r="B487" s="12" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A488" s="11">
+        <v>98337</v>
+      </c>
+      <c r="B488" s="12" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A489" s="11">
+        <v>98330</v>
+      </c>
+      <c r="B489" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A490" s="11">
+        <v>98334</v>
+      </c>
+      <c r="B490" s="12" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A491" s="11">
+        <v>98333</v>
+      </c>
+      <c r="B491" s="12" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A492" s="11">
+        <v>98433</v>
+      </c>
+      <c r="B492" s="12" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A493" s="11">
+        <v>98425</v>
+      </c>
+      <c r="B493" s="12" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A494" s="11">
+        <v>98424</v>
+      </c>
+      <c r="B494" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A495" s="11">
+        <v>98426</v>
+      </c>
+      <c r="B495" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A496" s="11">
+        <v>98428</v>
+      </c>
+      <c r="B496" s="12" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A497" s="11">
+        <v>98435</v>
+      </c>
+      <c r="B497" s="12" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A498" s="11">
+        <v>98430</v>
+      </c>
+      <c r="B498" s="12" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A499" s="11">
+        <v>98432</v>
+      </c>
+      <c r="B499" s="12" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A500" s="11">
+        <v>98429</v>
+      </c>
+      <c r="B500" s="12" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A501" s="11">
+        <v>98423</v>
+      </c>
+      <c r="B501" s="12" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A502" s="11">
+        <v>98431</v>
+      </c>
+      <c r="B502" s="12" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A503" s="11">
+        <v>98434</v>
+      </c>
+      <c r="B503" s="12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A504" s="11">
+        <v>98427</v>
+      </c>
+      <c r="B504" s="12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A505" s="11">
+        <v>98436</v>
+      </c>
+      <c r="B505" s="12" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A506" s="11">
+        <v>98309</v>
+      </c>
+      <c r="B506" s="12" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A507" s="11">
+        <v>98308</v>
+      </c>
+      <c r="B507" s="12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A508" s="11">
+        <v>98307</v>
+      </c>
+      <c r="B508" s="12" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A509" s="11">
+        <v>98303</v>
+      </c>
+      <c r="B509" s="12" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A510" s="11">
+        <v>98301</v>
+      </c>
+      <c r="B510" s="12" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A511" s="11">
+        <v>98306</v>
+      </c>
+      <c r="B511" s="12" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A512" s="11">
+        <v>98304</v>
+      </c>
+      <c r="B512" s="12" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A513" s="11">
+        <v>98302</v>
+      </c>
+      <c r="B513" s="12" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A514" s="11">
+        <v>98305</v>
+      </c>
+      <c r="B514" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A515" s="11">
+        <v>98299</v>
+      </c>
+      <c r="B515" s="12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A516" s="11">
+        <v>98300</v>
+      </c>
+      <c r="B516" s="12" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A517" s="11">
+        <v>98292</v>
+      </c>
+      <c r="B517" s="12" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A518" s="11">
+        <v>98283</v>
+      </c>
+      <c r="B518" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A519" s="11">
+        <v>98297</v>
+      </c>
+      <c r="B519" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A520" s="11">
+        <v>98293</v>
+      </c>
+      <c r="B520" s="12" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A521" s="11">
+        <v>98294</v>
+      </c>
+      <c r="B521" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A522" s="11">
+        <v>98295</v>
+      </c>
+      <c r="B522" s="12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A523" s="11">
+        <v>98288</v>
+      </c>
+      <c r="B523" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A524" s="11">
+        <v>98281</v>
+      </c>
+      <c r="B524" s="12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A525" s="11">
+        <v>98287</v>
+      </c>
+      <c r="B525" s="12" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A526" s="11">
+        <v>98286</v>
+      </c>
+      <c r="B526" s="12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A527" s="11">
+        <v>98282</v>
+      </c>
+      <c r="B527" s="12" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A528" s="11">
+        <v>98289</v>
+      </c>
+      <c r="B528" s="12" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A529" s="11">
+        <v>98296</v>
+      </c>
+      <c r="B529" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A530" s="11">
+        <v>98290</v>
+      </c>
+      <c r="B530" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A531" s="11">
+        <v>98285</v>
+      </c>
+      <c r="B531" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A532" s="11">
+        <v>98291</v>
+      </c>
+      <c r="B532" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A533" s="11">
+        <v>98284</v>
+      </c>
+      <c r="B533" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A534" s="11">
+        <v>98317</v>
+      </c>
+      <c r="B534" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A535" s="11">
+        <v>98311</v>
+      </c>
+      <c r="B535" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A536" s="11">
+        <v>98313</v>
+      </c>
+      <c r="B536" s="12" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A537" s="11">
+        <v>98310</v>
+      </c>
+      <c r="B537" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A538" s="11">
+        <v>98318</v>
+      </c>
+      <c r="B538" s="12" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A539" s="11">
+        <v>98316</v>
+      </c>
+      <c r="B539" s="12" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A540" s="11">
+        <v>98315</v>
+      </c>
+      <c r="B540" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A541" s="11">
+        <v>98314</v>
+      </c>
+      <c r="B541" s="12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A542" s="11">
+        <v>98312</v>
+      </c>
+      <c r="B542" s="12" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A543" s="11">
+        <v>98319</v>
+      </c>
+      <c r="B543" s="12" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A544" s="11">
+        <v>98363</v>
+      </c>
+      <c r="B544" s="12" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A545" s="11">
+        <v>98370</v>
+      </c>
+      <c r="B545" s="12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A546" s="11">
+        <v>98369</v>
+      </c>
+      <c r="B546" s="12" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A547" s="11">
+        <v>98372</v>
+      </c>
+      <c r="B547" s="12" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A548" s="11">
+        <v>98364</v>
+      </c>
+      <c r="B548" s="12" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A549" s="11">
+        <v>98368</v>
+      </c>
+      <c r="B549" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A550" s="11">
+        <v>98365</v>
+      </c>
+      <c r="B550" s="12" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A551" s="11">
+        <v>98366</v>
+      </c>
+      <c r="B551" s="12" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A552" s="11">
+        <v>98367</v>
+      </c>
+      <c r="B552" s="12" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A553" s="11">
+        <v>98371</v>
+      </c>
+      <c r="B553" s="12" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A554" s="11">
+        <v>98348</v>
+      </c>
+      <c r="B554" s="12" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A555" s="11">
+        <v>98346</v>
+      </c>
+      <c r="B555" s="12" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A556" s="11">
+        <v>98344</v>
+      </c>
+      <c r="B556" s="12" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A557" s="11">
+        <v>98351</v>
+      </c>
+      <c r="B557" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A558" s="11">
+        <v>98347</v>
+      </c>
+      <c r="B558" s="12" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A559" s="11">
+        <v>98345</v>
+      </c>
+      <c r="B559" s="12" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A560" s="11">
+        <v>98343</v>
+      </c>
+      <c r="B560" s="12" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A561" s="11">
+        <v>98350</v>
+      </c>
+      <c r="B561" s="12" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A562" s="11">
+        <v>98349</v>
+      </c>
+      <c r="B562" s="12" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A563" s="11">
+        <v>98342</v>
+      </c>
+      <c r="B563" s="12" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A564" s="11">
+        <v>98447</v>
+      </c>
+      <c r="B564" s="12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A565" s="11">
+        <v>98440</v>
+      </c>
+      <c r="B565" s="12" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A566" s="11">
+        <v>98451</v>
+      </c>
+      <c r="B566" s="12" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A567" s="11">
+        <v>98449</v>
+      </c>
+      <c r="B567" s="12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A568" s="11">
+        <v>98437</v>
+      </c>
+      <c r="B568" s="12" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A569" s="11">
+        <v>98442</v>
+      </c>
+      <c r="B569" s="12" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A570" s="11">
+        <v>98446</v>
+      </c>
+      <c r="B570" s="12" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A571" s="11">
+        <v>98444</v>
+      </c>
+      <c r="B571" s="12" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A572" s="11">
+        <v>98438</v>
+      </c>
+      <c r="B572" s="12" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A573" s="11">
+        <v>98441</v>
+      </c>
+      <c r="B573" s="12" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A574" s="11">
+        <v>98450</v>
+      </c>
+      <c r="B574" s="12" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A575" s="11">
+        <v>98439</v>
+      </c>
+      <c r="B575" s="12" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A576" s="11">
+        <v>98443</v>
+      </c>
+      <c r="B576" s="12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A577" s="11">
+        <v>98445</v>
+      </c>
+      <c r="B577" s="12" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A578" s="11">
+        <v>98448</v>
+      </c>
+      <c r="B578" s="12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A579" s="11">
+        <v>98414</v>
+      </c>
+      <c r="B579" s="12" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A580" s="11">
+        <v>98412</v>
+      </c>
+      <c r="B580" s="12" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A581" s="11">
+        <v>98411</v>
+      </c>
+      <c r="B581" s="12" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A582" s="11">
+        <v>98421</v>
+      </c>
+      <c r="B582" s="12" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A583" s="11">
+        <v>98415</v>
+      </c>
+      <c r="B583" s="12" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A584" s="11">
+        <v>98410</v>
+      </c>
+      <c r="B584" s="12" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A585" s="11">
+        <v>98407</v>
+      </c>
+      <c r="B585" s="12" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A586" s="11">
+        <v>98408</v>
+      </c>
+      <c r="B586" s="12" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A587" s="11">
+        <v>98416</v>
+      </c>
+      <c r="B587" s="12" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A588" s="11">
+        <v>98409</v>
+      </c>
+      <c r="B588" s="12" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A589" s="11">
+        <v>98417</v>
+      </c>
+      <c r="B589" s="12" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A590" s="11">
+        <v>98413</v>
+      </c>
+      <c r="B590" s="12" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A591" s="11">
+        <v>98420</v>
+      </c>
+      <c r="B591" s="12" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A592" s="11">
+        <v>98418</v>
+      </c>
+      <c r="B592" s="12" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A593" s="13">
+        <v>98419</v>
+      </c>
+      <c r="B593" s="14" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/gram_panchayat_reservation.xlsx
+++ b/gram_panchayat_reservation.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anind\gram_panchayat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56375533-E4A0-409B-A7CA-6A918370EA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E0798E-A7C2-4CF2-9596-6ACBE74DE4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="gp_code" sheetId="2" r:id="rId2"/>
+    <sheet name="gp_code" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -1595,18 +1594,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
